--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">246772</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>2800</v>
+        <v>5875</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">717938, 7644227</t>
+          <t xml:space="preserve">717951, 2380858</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>303</v>
+        <v>490</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">717951, 2380858</t>
+          <t xml:space="preserve">717953, 2381215</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F12">
-        <v>490</v>
+        <v>1394</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">717952, 2381218</t>
+          <t xml:space="preserve">717965, 2381219</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F13">
-        <v>476</v>
+        <v>596</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">717953, 2381215</t>
+          <t xml:space="preserve">717971, 2370955</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F14">
-        <v>1394</v>
+        <v>1375</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">717965, 2381219</t>
+          <t xml:space="preserve">717972, 2370956</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F15">
-        <v>596</v>
+        <v>403</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,30 +781,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">717970, 2370954</t>
+          <t xml:space="preserve">2381217, 100749912</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>4496</v>
+        <v>363</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100144275</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -831,30 +831,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">717971, 2370955</t>
+          <t xml:space="preserve">717973, 2370957</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F17">
-        <v>1375</v>
+        <v>3096</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200052253</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -881,30 +881,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">717972, 2370956</t>
+          <t xml:space="preserve">717970, 2370954</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F18">
-        <v>403</v>
+        <v>4496</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056359</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">717973, 2370957</t>
+          <t xml:space="preserve">717952, 2381218</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="F19">
-        <v>3096</v>
+        <v>476</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311065041</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -981,35 +981,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">717938, 7644227</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F20">
-        <v>2969</v>
+        <v>303</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311217548</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1031,35 +1031,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>916</v>
+        <v>341</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1081,35 +1081,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381217, 100749912</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F22">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100144275</t>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">2367843</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="F23">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311259586</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367182</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F25">
-        <v>769</v>
+        <v>669</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259590</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367843</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F26">
-        <v>458</v>
+        <v>500</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259586</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1336,20 +1336,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>4057</v>
+        <v>6457</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259593</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,20 +1381,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F28">
-        <v>368</v>
+        <v>2969</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F29">
-        <v>669</v>
+        <v>916</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1481,20 +1481,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>500</v>
+        <v>6610</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1536,15 +1536,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F31">
-        <v>6457</v>
+        <v>4057</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1586,15 +1586,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F32">
-        <v>6610</v>
+        <v>1595</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265094</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2366692</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>1595</v>
+        <v>613</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265957</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366692</t>
+          <t xml:space="preserve">2367182</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="F34">
-        <v>613</v>
+        <v>769</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265957</t>
+          <t xml:space="preserve">311269865</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">246772</t>
+          <t xml:space="preserve">100019618</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="F38">
-        <v>5875</v>
+        <v>1306</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272829</t>
+          <t xml:space="preserve">311279819</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-14</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019618</t>
+          <t xml:space="preserve">2367211</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="F39">
-        <v>1306</v>
+        <v>430</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279819</t>
+          <t xml:space="preserve">311279821</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367211</t>
+          <t xml:space="preserve">2366957</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="F40">
-        <v>430</v>
+        <v>744</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279821</t>
+          <t xml:space="preserve">311286269</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366957</t>
+          <t xml:space="preserve">2369150</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,11 +2040,11 @@
         </is>
       </c>
       <c r="F41">
-        <v>744</v>
+        <v>1941</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286269</t>
+          <t xml:space="preserve">311286265</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369150</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F42">
-        <v>1941</v>
+        <v>2800</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286265</t>
+          <t xml:space="preserve">311286266</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">

--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:L70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ulvemosen 5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1310679</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>304</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gutfeldtsvej 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2366600</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1278</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gutfeldtsvej 6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2366726</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1519</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>600</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>454</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 4E</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>294</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">246772</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>5875</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kokkedal Alle 9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">717933, 2370872</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>427</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kokkedal Alle 9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">717933, 2370872</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>366</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungsted Strandvej 120</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">717951, 2380858</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>490</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungsted Havn 1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">717953, 2381215</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1394</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungsted Havn 28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">717965, 2381219</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>596</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 7D</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">717971, 2370955</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>1375</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 7C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">717972, 2370956</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>403</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungsted Havn 8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2381217, 100749912</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>363</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">100144275</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 7A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">717973, 2370957</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>3096</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">200052253</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 9</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">717970, 2370954</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>4496</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">200056359</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungsted Havn 32</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">717952, 2381218</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>476</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311065041</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungsted Havn 34</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">717938, 7644227</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>303</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311217548</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alsvej 83</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2368570</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>341</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311239833</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alsvej 83</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2368570</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>393</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311239833</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Usserød Kongevej 45</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367843</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>458</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311259586</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahornvej 50A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367722</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>368</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311265087</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahornvej 50B</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367722</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>669</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311265087</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ahornvej 50C</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367722</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>500</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311265087</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>6457</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265099</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 11A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>2969</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311265093</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>916</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311265093</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 11A</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>6610</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265094</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 11B</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>4057</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311265093</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>1595</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265099</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selmersvej 13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2366692</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>613</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311265957</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367182</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>769</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311269865</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 4</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2381983</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>521</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311270049</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungstedvej 31</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>267</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311269866</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369157</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>476</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311272832</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Breeltevej 3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">100019618</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1306</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311279819</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gasværksvej 1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367211</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>430</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311279821</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skovvænget 36</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2366957</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>744</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311286269</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sophielund 25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369150</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>1941</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311286265</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 8</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2381978</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>2800</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311286266</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungstedvej 1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367324</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>2151</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311288806</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsvej 52</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369817</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1351</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311288805</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsvej 52</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369817</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>1171</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311288805</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selmersvej 6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>1691</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311289939</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selmersvej 6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>3265</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311289940</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selmersvej 6</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>1610</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311289942</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selmersvej 6</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>2388</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311289943</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Selmersvej 6</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>474</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311289945</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>8807</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311298940</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>2450</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311298940</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>1637</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311298938</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionalle 12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2381978</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>6712</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311304707</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-03-23</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>1507</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311306137</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311306140</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>2099</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311308266</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>3262</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311308262</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>614</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311308267</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalsparkvej 4N</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>408</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311420783</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-02-04</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rungstedvej 23</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2366696</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>445</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311892520</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367940</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>350</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311893229</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2367940</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>2855</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311893225</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mariehøj Alle 1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">7951098</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>690</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311912380</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundevej 26</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">9153647</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>840</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311915684</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Byvej 10</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>1343</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Byvej 10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>929</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Byvej 10</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>2007</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Byvej 10</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>599</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl Byvej 10</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>3389</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,39 +4171,49 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundevej 19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>2456</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J70"/>
+  <autoFilter ref="A1:L70"/>
 </worksheet>
 </file>
--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 5</t>
+          <t xml:space="preserve">Gutfeldtsvej 2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310679</t>
+          <t xml:space="preserve">2366600</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>304</v>
+        <v>1278</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gutfeldtsvej 2</t>
+          <t xml:space="preserve">Gutfeldtsvej 6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366600</t>
+          <t xml:space="preserve">2366726</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>1278</v>
+        <v>1519</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gutfeldtsvej 6</t>
+          <t xml:space="preserve">Kokkedal Alle 9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366726</t>
+          <t xml:space="preserve">717933, 2370872</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H4">
-        <v>1519</v>
+        <v>427</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Kokkedal Alle 9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,7 +281,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">717933, 2370872</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="H5">
-        <v>600</v>
+        <v>366</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Rungsted Havn 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">717953, 2381215</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H6">
-        <v>454</v>
+        <v>1394</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4E</t>
+          <t xml:space="preserve">Rungsted Havn 28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">717965, 2381219</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H7">
-        <v>294</v>
+        <v>596</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekstorvet 1</t>
+          <t xml:space="preserve">Rungsted Strandvej 120</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">246772</t>
+          <t xml:space="preserve">717951, 2380858</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>5875</v>
+        <v>490</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Alle 9</t>
+          <t xml:space="preserve">Stadionalle 7C</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">717933, 2370872</t>
+          <t xml:space="preserve">717972, 2370956</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H9">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Alle 9</t>
+          <t xml:space="preserve">Stadionalle 7D</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">717933, 2370872</t>
+          <t xml:space="preserve">717971, 2370955</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H10">
-        <v>366</v>
+        <v>1375</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Strandvej 120</t>
+          <t xml:space="preserve">Ulvemosen 5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">717951, 2380858</t>
+          <t xml:space="preserve">1310679</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="H11">
-        <v>490</v>
+        <v>304</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 1</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">717953, 2381215</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H12">
-        <v>1394</v>
+        <v>600</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 28</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">717965, 2381219</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H13">
-        <v>596</v>
+        <v>454</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7D</t>
+          <t xml:space="preserve">Ådalsparkvej 4E</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">717971, 2370955</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H14">
-        <v>1375</v>
+        <v>294</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7C</t>
+          <t xml:space="preserve">Rungsted Havn 8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,30 +881,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">717972, 2370956</t>
+          <t xml:space="preserve">2381217, 100749912</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H15">
-        <v>403</v>
+        <v>363</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100144275</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 8</t>
+          <t xml:space="preserve">Stadionalle 7A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,25 +941,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381217, 100749912</t>
+          <t xml:space="preserve">717973, 2370957</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H16">
-        <v>363</v>
+        <v>3096</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">100144275</t>
+          <t xml:space="preserve">200052253</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7A</t>
+          <t xml:space="preserve">Stadionalle 9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,25 +1001,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">717973, 2370957</t>
+          <t xml:space="preserve">717970, 2370954</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H17">
-        <v>3096</v>
+        <v>4496</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052253</t>
+          <t xml:space="preserve">200056359</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-23</t>
+          <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 9</t>
+          <t xml:space="preserve">Rungsted Havn 32</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,25 +1061,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">717970, 2370954</t>
+          <t xml:space="preserve">717952, 2381218</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H18">
-        <v>4496</v>
+        <v>476</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056359</t>
+          <t xml:space="preserve">311065041</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-30</t>
+          <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 32</t>
+          <t xml:space="preserve">Rungsted Havn 34</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,35 +1121,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">717952, 2381218</t>
+          <t xml:space="preserve">717938, 7644227</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H19">
-        <v>476</v>
+        <v>303</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311065041</t>
+          <t xml:space="preserve">311217548</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-16</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1171,35 +1171,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 34</t>
+          <t xml:space="preserve">Alsvej 83</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">717938, 7644227</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217548</t>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1246,11 +1246,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H21">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Usserød Kongevej 45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,25 +1301,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">2367843</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>393</v>
+        <v>458</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311259586</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usserød Kongevej 45</t>
+          <t xml:space="preserve">Ahornvej 50A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367843</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="H23">
-        <v>458</v>
+        <v>368</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259586</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50A</t>
+          <t xml:space="preserve">Ahornvej 50B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1426,11 +1426,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H24">
-        <v>368</v>
+        <v>669</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50B</t>
+          <t xml:space="preserve">Ahornvej 50C</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1486,11 +1486,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H25">
-        <v>669</v>
+        <v>500</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,30 +1531,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50C</t>
+          <t xml:space="preserve">Stadionalle 11A</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H26">
-        <v>500</v>
+        <v>2969</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Stadionalle 11A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1606,15 +1606,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H27">
-        <v>6457</v>
+        <v>6610</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265094</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Stadionalle 11B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1666,11 +1666,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H28">
-        <v>2969</v>
+        <v>4057</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1726,15 +1726,15 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H29">
-        <v>916</v>
+        <v>6457</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1786,15 +1786,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H30">
-        <v>6610</v>
+        <v>916</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265094</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11B</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1846,15 +1846,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H31">
-        <v>4057</v>
+        <v>1595</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,35 +1891,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Selmersvej 13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2366692</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>1595</v>
+        <v>613</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265957</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 13</t>
+          <t xml:space="preserve">Rungstedvej 31</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,25 +1961,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366692</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H33">
-        <v>613</v>
+        <v>267</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265957</t>
+          <t xml:space="preserve">311269866</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 31</t>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,25 +2141,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">246772</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>267</v>
+        <v>5875</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269866</t>
+          <t xml:space="preserve">311272829</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286266</t>
+          <t xml:space="preserve">311286267</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306140</t>
+          <t xml:space="preserve">311306137</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">

--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286267</t>
+          <t xml:space="preserve">311286266</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">

--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:M70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">BygTechA/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">LuVa Consult APS</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">LuVa Consult APS</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">BF Byggeservice ApS</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-23</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3294,20 +3564,25 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306137</t>
+          <t xml:space="preserve">311306142</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-04</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,21 +4544,26 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L70"/>
+  <autoFilter ref="A1:M70"/>
 </worksheet>
 </file>
--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265094</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306142</t>
+          <t xml:space="preserve">311306137</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
